--- a/unified/shell-pywebview/dist/core/报表采集系统_比较配置.xlsx
+++ b/unified/shell-pywebview/dist/core/报表采集系统_比较配置.xlsx
@@ -10,8 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="指标参照" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="机构参照" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="警戒区间" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特殊指标-自定义" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="复杂校验-自定义" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校验规则" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,17 +437,17 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>是否不转换单位</t>
+          <t>不转换单位</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>是否与大集中核对</t>
+          <t>大集中核对</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>大集中报表查询指标名称</t>
+          <t>大集中指标名称</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -458,17 +457,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>表单</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>频度</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>核对要求</t>
+          <t>备注</t>
         </is>
       </c>
     </row>
@@ -494,16 +483,6 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
           <t>有变动需说明，机构基础信息一般不会变动；</t>
         </is>
       </c>
@@ -530,16 +509,6 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
           <t>有变动需说明，机构基础信息一般不会变动；</t>
         </is>
       </c>
@@ -566,16 +535,6 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
           <t>有变动需说明，机构基础信息一般不会变动；</t>
         </is>
       </c>
@@ -602,16 +561,6 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
           <t>有变动需说明，机构基础信息一般不会变动；</t>
         </is>
       </c>
@@ -638,16 +587,6 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
           <t>有变动需说明，机构基础信息一般不会变动；</t>
         </is>
       </c>
@@ -674,16 +613,6 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
           <t>有变动需说明，机构基础信息一般不会变动；</t>
         </is>
       </c>
@@ -708,17 +637,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -742,16 +661,6 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
           <t>有变动需说明，机构基础信息一般不会变动；</t>
         </is>
       </c>
@@ -778,16 +687,6 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
           <t>有变动需说明，需核实是否变更；</t>
         </is>
       </c>
@@ -814,16 +713,6 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
           <t>有变动需说明，需核实是否变更；</t>
         </is>
       </c>
@@ -850,16 +739,6 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
           <t>有变动需说明，机构基础信息一般不会变动；</t>
         </is>
       </c>
@@ -886,16 +765,6 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
           <t>有变动需说明，机构基础信息一般不会变动；</t>
         </is>
       </c>
@@ -922,16 +791,6 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
           <t>有变动需说明，机构基础信息一般不会变动；</t>
         </is>
       </c>
@@ -958,16 +817,6 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
           <t>有变动需说明，需核实是否变更；</t>
         </is>
       </c>
@@ -994,16 +843,6 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
           <t>有变动需说明，需核实是否变更；</t>
         </is>
       </c>
@@ -1030,16 +869,6 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
           <t>有变动需说明，需核实是否变更；</t>
         </is>
       </c>
@@ -1076,17 +905,7 @@
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1110,16 +929,6 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
           <t>有变动需说明，需核实是否变更；</t>
         </is>
       </c>
@@ -1146,16 +955,6 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
           <t>有变动需说明，需核实是否变更；</t>
         </is>
       </c>
@@ -1182,16 +981,6 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
           <t>有变动需说明，需核实是否变更；</t>
         </is>
       </c>
@@ -1218,16 +1007,6 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
           <t>有变动需说明，需核实是否变更；</t>
         </is>
       </c>
@@ -1254,16 +1033,6 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
           <t>有变动需说明，需核实是否变更；</t>
         </is>
       </c>
@@ -1290,16 +1059,6 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
           <t>有变动需说明，需核实是否变更；</t>
         </is>
       </c>
@@ -1326,16 +1085,6 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
           <t>有变动需说明，需核实是否变更；</t>
         </is>
       </c>
@@ -1362,16 +1111,6 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
           <t>有变动需说明，需核实是否变更；</t>
         </is>
       </c>
@@ -1398,16 +1137,6 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
           <t>有变动需说明，需核实是否变更；</t>
         </is>
       </c>
@@ -1434,16 +1163,6 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
           <t>有变动需说明，需核实是否变更；</t>
         </is>
       </c>
@@ -1472,17 +1191,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1508,17 +1217,7 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1544,17 +1243,7 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1580,17 +1269,7 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1616,17 +1295,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1652,17 +1321,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1688,17 +1347,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1724,17 +1373,7 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1760,17 +1399,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1796,17 +1425,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>20201</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1836,17 +1455,7 @@
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1876,17 +1485,7 @@
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1908,17 +1507,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1940,17 +1529,7 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1980,17 +1559,7 @@
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2012,17 +1581,7 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2044,17 +1603,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2076,17 +1625,7 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2108,17 +1647,7 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2140,17 +1669,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2172,17 +1691,7 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2204,17 +1713,7 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2236,17 +1735,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2268,17 +1757,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2300,17 +1779,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2332,17 +1801,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2372,17 +1831,7 @@
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2414,16 +1863,6 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -2458,16 +1897,6 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -2502,16 +1931,6 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -2546,16 +1965,6 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -2590,16 +1999,6 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -2634,16 +2033,6 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -2678,16 +2067,6 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -2722,16 +2101,6 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -2766,16 +2135,6 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -2810,16 +2169,6 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -2854,16 +2203,6 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -2898,16 +2237,6 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -2942,16 +2271,6 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -2986,16 +2305,6 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3030,16 +2339,6 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3074,16 +2373,6 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3118,16 +2407,6 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3162,16 +2441,6 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3206,16 +2475,6 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3250,16 +2509,6 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3294,16 +2543,6 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3338,16 +2577,6 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3382,16 +2611,6 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3426,16 +2645,6 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3470,16 +2679,6 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3514,16 +2713,6 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3558,16 +2747,6 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3602,16 +2781,6 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3646,16 +2815,6 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3690,16 +2849,6 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3734,16 +2883,6 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3778,16 +2917,6 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3822,16 +2951,6 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3866,16 +2985,6 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3910,16 +3019,6 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3954,16 +3053,6 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -3998,16 +3087,6 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -4042,16 +3121,6 @@
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -4086,16 +3155,6 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -4130,16 +3189,6 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -4174,16 +3223,6 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -4218,16 +3257,6 @@
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -4262,16 +3291,6 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -4306,16 +3325,6 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -4350,16 +3359,6 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -4394,16 +3393,6 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
       </c>
@@ -4437,16 +3426,6 @@
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
-        <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
         <is>
           <t>与大集中3301本外币数值保持一致。对于系统校验的提示，与大集中核对结果进行对比。</t>
         </is>
@@ -4472,17 +3451,7 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4504,17 +3473,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4536,17 +3495,7 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4568,17 +3517,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>季</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4617,7 +3556,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>归属行</t>
+          <t>地区</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -4910,222 +3849,157 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>序号</t>
+          <t>变幅下限（小数，0.3=30%）</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>变幅下限（小数，0.3=30%）</t>
+          <t>备注</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>是否整行填充</t>
+          <t>整行填充</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" t="n">
         <v>-0.96</v>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>降幅(-96%,-90%],缩小10倍-100倍</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>降幅(-96%,-90%],缩小10倍-100倍</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="A3" t="n">
         <v>-0.9</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>降幅(-90%,-80%],缩小5倍-10倍</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="A4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>降幅(-80%,50%],缩小1倍-5倍</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="A5" t="n">
         <v>-0.5</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>降幅(-50%,-30%],缩小1倍以内</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="A6" t="n">
         <v>-0.3</v>
       </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+      <c r="A7" t="n">
         <v>0</v>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="A8" t="n">
         <v>0.3</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>增幅[30%,50%)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+      <c r="A9" t="n">
         <v>0.5</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>增幅[50%,1倍)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+      <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>增幅[1倍,5倍)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+      <c r="A11" t="n">
         <v>5</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>增幅[5倍,10倍)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>增幅[10倍,96倍)</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>增幅[10倍,96倍)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+      <c r="A13" t="n">
         <v>96</v>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>近增幅100倍以上，请核实</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>近增幅100倍以上，请核实</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -5142,75 +4016,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>指标代码</t>
+          <t>规则编号</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>指标名</t>
+          <t>类型</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>规则内容</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>级别</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>禁用</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>备注</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>人民币阀值(亿元)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>美元合计阀值(亿美元)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>数据属性</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>说明/比较指标</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>表单</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>详细说明</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>绝对值变幅（%）</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>禁用</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20203001</t>
+          <t>R001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>一、营业收入</t>
+          <t>累计不降(当年)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5218,1637 +4072,552 @@
           <t>当年累计指标比上期不应减少。</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>20203003,20203004,20203005,20203006,20203007,20203008,20203009,20203010,20203011,20203012,20203013,20203014,20203016,20203017,20203018,20203020,20203021,20203022,20203023,20203024,20203025,20203049,20203026,20203028,20203029,20203030,20203031,20203032,20203033,20203050,20203051,20203034,20203036,20203037,20203039,20203044</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>提示</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>旧表停用代码：20203001、20203002、20203015、20203019、20203027、20203035、20203038、20203040、20203041</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20203002</t>
+          <t>R002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.利息净收入</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>核心一级资本充足率低于5.5%，接近监管底线</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[20203045] &lt; 0.055 * [20203048]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>核实</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20203003</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>利息收入</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>一级资本充足率低于6.5%，接近监管底线</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[20203046] &lt; 0.065 * [20203048]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>核实</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20203004</t>
+          <t>R004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>金融机构往来利息收入</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>资本充足率低于8.5%，接近监管底线</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[20203047] &lt; 0.085 * [20203048]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>核实</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20203005</t>
+          <t>R005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>其中：系统内往来利息收入</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>资本层级关系异常（核心/一级/总资本）</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>OR([20203045] &gt; [20203046] , [20203046] &gt; [20203047])</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>错误</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20203006</t>
+          <t>R006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>各项贷款利息收入</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>资产负债表不平衡</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[20202003] &lt;&gt; [20202004] + [20202005]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>错误</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20203007</t>
+          <t>R007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>债券利息收入</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+          <t>应用资本底线及校准后的风险加权资产合计大于总资产</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[20203048] &gt; [20202003]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>核实</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20203008</t>
+          <t>R008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>其他利息收入</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t>应用资本底线及校准后的风险加权资产合计占比总资产过低，小于40%；</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>[20203048] &lt; 0.4 * [20202003]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>核实</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20203009</t>
+          <t>R009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>利息支出</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+          <t>应用资本底线及校准后的风险加权资产合计占比总资产过高，大于80%；</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[20203048] &gt; 0.8 * [20202003]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>核实</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20203010</t>
+          <t>R010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>金融机构往来利息支出</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+          <t>五级分类合计不等于贷款总额</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>[20202010] + [20202011] + [20202012] + [20202013] + [20202014] &lt;&gt; [20202002]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>错误</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20203011</t>
+          <t>R011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>其中：系统内往来利息支出</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+          <t>逾期90天以上贷款大于逾期贷款</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>[20202016] &gt; [20202015]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>错误</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20203012</t>
+          <t>R012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>各项存款利息支出</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+          <t>逾期贷款大于贷款总额</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>[20202015] &gt; [20202002]</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>错误</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20203013</t>
+          <t>R013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>债券利息支出</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+          <t>不良贷款大于贷款总额</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>[20202012] + [20202013] + [20202014] &gt; [20202002]</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>错误</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20203014</t>
+          <t>R014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>其他利息支出</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+          <t>拨备覆盖率低于100%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>[20202017] &lt; ([20202012] + [20202013] + [20202014])</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>核实</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20203015</t>
+          <t>R015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2.手续费及佣金净收入</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+          <t>流动性比例低于30%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>[20202008] &lt; 0.3 * [20202009]</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>核实</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20203016</t>
+          <t>R016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>手续费及佣金收入</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+          <t>存贷比超过90%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>[20202002] &gt; 0.9 * [20202001]</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>核实</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20203017</t>
+          <t>R017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>手续费及佣金支出</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+          <t>权益占比过低，杠杆偏高</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>[20202005] &lt; 0.055 * [20202003]</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>核实</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20203018</t>
+          <t>R018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3.租赁收益</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+          <t>不良未降但拨备下降</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AND([20202017] &lt; {20202017} , ([20202012] + [20202013] + [20202014]) &gt;= ({20202012} + {20202013} + {20202014}))</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>提示</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20203019</t>
+          <t>R019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4.投资收益</t>
+          <t>表达式</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+          <t>存款下降但贷款上升，流动性承压</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AND([20202001] &lt; {20202001} , [20202002] &gt; {20202002})</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>提示</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20203020</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>债券投资收益</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>20203021</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>股权投资收益</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>20203022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>其他投资收益</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>20203023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>5.公允价值变动收益</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>20203024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>6.汇兑净收益</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>20203025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>7.资产处置收益</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>20203049</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>8.其他收益</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>20203026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>9.其他业务收入</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>20203027</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>二、营业支出</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>20203028</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1.业务及管理费</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>20203029</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>其中:职工工资</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>20203030</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>福利费</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>20203031</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>住房公积金和住房补贴</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>20203032</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2.税金及附加</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>20203033</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>3.资产减值损失</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>20203050</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>4.信用减值损失</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>20203051</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>5.其他资产减值损失</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>20203034</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>6.其他业务支出</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>20203035</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>三、营业利润</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>20203036</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>营业外收入（加）</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>20203037</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>营业外支出（减）</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>20203038</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>四、利润总额</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>20203039</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>所得税（减）</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>20203040</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>五、净利润</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>20203041</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>年度损益调整（加）</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>20203044</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>应纳增值税</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>当年累计指标比上期不应减少。</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>校验表单</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>校验描述</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>校验规则</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>取反标识</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Thd值(万元)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>禁用</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A0000</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>XX</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>[机构名称，地区，机构类别，指标代码，频度]&gt;0</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>表1-1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>测试</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>[,,,C203-R001C001,]&lt;0</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>核心一级资本充足率低于5.5%，接近监管底线</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>[,,,20203045,] &lt; 0.055 * [,,,20203048,]</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>一级资本充足率低于6.5%，接近监管底线</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>[,,,20203046,] &lt; 0.065 * [,,,20203048,]</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>资本充足率低于8.5%，接近监管底线</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>[,,,20203047,] &lt; 0.085 *[,,,20203048,]</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>资本层级关系异常（核心/一级/总资本）</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>or([,,,20203045,] &gt; [,,,20203046,] , [,,,20203046,] &gt; [,,,20203047,])</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>资产负债表不平衡</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>[,,,20202003,] &lt;&gt; [,,,20202004,] + [,,,20202005,]</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>应用资本底线及校准后的风险加权资产合计大于总资产</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>[,,,20203048,] &gt; [,,,20202003,]</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>应用资本底线及校准后的风险加权资产合计占比总资产过低，小于40%；</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>[,,,20203048,] &lt; 0.4 * [,,,20202003,]</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>20203</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>应用资本底线及校准后的风险加权资产合计占比总资产过高，大于80%；</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>[,,,20203048,] &gt; 0.8 * [,,,20202003,]</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>五级分类合计不等于贷款总额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>[,,,20202010,]+[,,,20202011,]+[,,,20202012,]+[,,,20202013,]+[,,,20202014,] &lt;&gt; [,,,20202002,]</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>逾期90天以上贷款大于逾期贷款</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>[,,,20202016,] &gt; [,,,20202015,]</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>逾期贷款大于贷款总额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>[,,,20202015,] &gt; [,,,20202002,]</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>不良贷款大于贷款总额</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>[,,,20202012,]+[,,,20202013,]+[,,,20202014,] &gt; [,,,20202002,]</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>拨备覆盖率低于100%</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>[,,,20202017,] &lt; ([,,,20202012,]+[,,,20202013,]+[,,,20202014,])</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>流动性比例低于30%</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>[,,,20202008,] &lt; 0.3 * [,,,20202009,]</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>存贷比超过90%</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>[,,,20202002,] &gt; 0.9 *[,,,20202001,]</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>权益占比过低，杠杆偏高</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[,,,20202005,] &lt; 0.055 *[,,,20202003,]</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>不良未降但拨备下降</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AND([,,,20202017,] &lt; {,,,20202017,} , ([,,,20202012,]+[,,,20202013,]+[,,,20202014,]) &gt;= ({,,,20202012,}+{,,,20202013,}+{,,,20202014,}))</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>存款下降但贷款上升，流动性承压</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AND([,,,20202001,] &lt; {,,,20202001,} , [,,,20202002,] &gt; {,,,20202002,})</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
